--- a/HR Employee Records Analysis Results.xlsx
+++ b/HR Employee Records Analysis Results.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\BL6PEPF00069866\EXCELCNV\712e19cf-9f52-4d78-81cf-af4a8caa2f4d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4ABF421-47B2-4F09-990E-0038B1592D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{444CE093-9D35-4287-9187-2BB1ED68B6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" activeTab="4" xr2:uid="{20B3D7EB-641B-4C41-9538-2E278A9236B1}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" firstSheet="4" xr2:uid="{20B3D7EB-641B-4C41-9538-2E278A9236B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Query 1" sheetId="2" r:id="rId1"/>
     <sheet name="Query 2" sheetId="3" r:id="rId2"/>
-    <sheet name="Query 3" sheetId="4" r:id="rId3"/>
-    <sheet name="Query 4" sheetId="5" r:id="rId4"/>
-    <sheet name="Query 5" sheetId="6" r:id="rId5"/>
-    <sheet name="Query 6" sheetId="1" r:id="rId6"/>
+    <sheet name="Query 3" sheetId="7" r:id="rId3"/>
+    <sheet name="Query 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Query 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Query 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Query 7" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="61">
   <si>
     <t>Department</t>
   </si>
@@ -58,6 +59,9 @@
     <t>Highest_Salary</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Finance</t>
   </si>
   <si>
@@ -113,6 +117,72 @@
   </si>
   <si>
     <t>Total_Salary_Expend</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>HireDate</t>
+  </si>
+  <si>
+    <t>PerformanceRating</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>TopSalary</t>
+  </si>
+  <si>
+    <t>Jennifer</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Linda</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>Garcia</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Williams</t>
   </si>
   <si>
     <t>AveragePerformanceRating</t>
@@ -163,7 +233,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -642,10 +712,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1001,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C361B70B-8C73-410E-BC2A-BBF4A3BA8F1F}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -1011,7 +1082,7 @@
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1027,16 +1098,19 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>265</v>
+        <v>180</v>
       </c>
       <c r="D2" s="2">
         <v>45124</v>
@@ -1045,15 +1119,15 @@
         <v>74644</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c r="D3" s="2">
         <v>45437</v>
@@ -1062,83 +1136,83 @@
         <v>74870</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>271</v>
+        <v>178</v>
       </c>
       <c r="D4" s="2">
-        <v>45188</v>
+        <v>45424</v>
       </c>
       <c r="E4" s="2">
         <v>74935</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>259</v>
+        <v>169</v>
       </c>
       <c r="D5" s="2">
         <v>45057</v>
       </c>
       <c r="E5" s="2">
-        <v>74863</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>74698</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>239</v>
+        <v>161</v>
       </c>
       <c r="D6" s="2">
         <v>45038</v>
       </c>
       <c r="E6" s="2">
-        <v>74905</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>74776</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2">
         <v>45034</v>
       </c>
       <c r="E7" s="2">
-        <v>74775</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>74705</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2">
         <v>45131</v>
@@ -1147,15 +1221,15 @@
         <v>74314</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="D9" s="2">
         <v>45062</v>
@@ -1164,38 +1238,38 @@
         <v>74935</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2">
         <v>80029</v>
       </c>
       <c r="E10" s="2">
-        <v>119593</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="D11" s="2">
         <v>45252</v>
       </c>
       <c r="E11" s="2">
-        <v>74794</v>
+        <v>74550</v>
       </c>
     </row>
   </sheetData>
@@ -1217,12 +1291,12 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1">
         <v>11332108.02</v>
@@ -1230,7 +1304,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>8907538.5199999996</v>
@@ -1238,7 +1312,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>8824006.1600000001</v>
@@ -1246,7 +1320,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
         <v>8211478.79</v>
@@ -1254,7 +1328,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
         <v>8044841.5300000003</v>
@@ -1262,7 +1336,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>7957924.7699999996</v>
@@ -1270,7 +1344,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
         <v>7759080.5999999996</v>
@@ -1278,7 +1352,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1">
         <v>7332376.6799999997</v>
@@ -1290,6 +1364,1220 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15ABDEB6-C70C-4665-89D0-650E72B144E0}">
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46077</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>114748</v>
+      </c>
+      <c r="G2" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3">
+        <v>45669</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>87443</v>
+      </c>
+      <c r="G3" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3">
+        <v>45730</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>117701</v>
+      </c>
+      <c r="G4" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3">
+        <v>45984</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>87221</v>
+      </c>
+      <c r="G5" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3">
+        <v>45697</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>82197</v>
+      </c>
+      <c r="G6" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3">
+        <v>45658</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>107782</v>
+      </c>
+      <c r="G7" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="3">
+        <v>45752</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>54658</v>
+      </c>
+      <c r="G8" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="3">
+        <v>45862</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>57159</v>
+      </c>
+      <c r="G9" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3">
+        <v>45663</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>68713</v>
+      </c>
+      <c r="G10" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3">
+        <v>45766</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>86173</v>
+      </c>
+      <c r="G11" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3">
+        <v>45887</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>106385</v>
+      </c>
+      <c r="G12" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="3">
+        <v>45987</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>104118</v>
+      </c>
+      <c r="G13" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="3">
+        <v>45662</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>91362</v>
+      </c>
+      <c r="G14" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="3">
+        <v>46218</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>92787</v>
+      </c>
+      <c r="G15" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="3">
+        <v>45873</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>116841</v>
+      </c>
+      <c r="G16" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="3">
+        <v>45856</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>56351</v>
+      </c>
+      <c r="G17" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="3">
+        <v>45761</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>58802</v>
+      </c>
+      <c r="G18" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="3">
+        <v>45922</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2">
+        <v>108190</v>
+      </c>
+      <c r="G19" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>88138</v>
+      </c>
+      <c r="G20" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="3">
+        <v>46151</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2">
+        <v>101464</v>
+      </c>
+      <c r="G21" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="3">
+        <v>45775</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2">
+        <v>100066</v>
+      </c>
+      <c r="G22" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="3">
+        <v>45820</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2">
+        <v>107829</v>
+      </c>
+      <c r="G23" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3">
+        <v>45821</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24" s="2">
+        <v>119410</v>
+      </c>
+      <c r="G24" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="3">
+        <v>45989</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2">
+        <v>57440</v>
+      </c>
+      <c r="G25" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="3">
+        <v>45778</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2">
+        <v>64943</v>
+      </c>
+      <c r="G26" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="3">
+        <v>45994</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2">
+        <v>72198</v>
+      </c>
+      <c r="G27" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="3">
+        <v>45751</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2">
+        <v>71070</v>
+      </c>
+      <c r="G28" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="3">
+        <v>46040</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2">
+        <v>85120</v>
+      </c>
+      <c r="G29" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="3">
+        <v>45853</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30" s="2">
+        <v>99361</v>
+      </c>
+      <c r="G30" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="3">
+        <v>46202</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2">
+        <v>99936</v>
+      </c>
+      <c r="G31" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="3">
+        <v>45783</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2">
+        <v>69498</v>
+      </c>
+      <c r="G32" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="3">
+        <v>45879</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33" s="2">
+        <v>69714</v>
+      </c>
+      <c r="G33" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="3">
+        <v>46135</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34" s="2">
+        <v>55391</v>
+      </c>
+      <c r="G34" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="3">
+        <v>45899</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2">
+        <v>54407</v>
+      </c>
+      <c r="G35" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="3">
+        <v>45718</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36" s="2">
+        <v>50036</v>
+      </c>
+      <c r="G36" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="3">
+        <v>45864</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37" s="2">
+        <v>52574</v>
+      </c>
+      <c r="G37" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="3">
+        <v>46167</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38" s="2">
+        <v>61384</v>
+      </c>
+      <c r="G38" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="3">
+        <v>45659</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39" s="2">
+        <v>62102</v>
+      </c>
+      <c r="G39" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="3">
+        <v>46031</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2">
+        <v>106858</v>
+      </c>
+      <c r="G40" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="3">
+        <v>45973</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+      <c r="F41" s="2">
+        <v>95386</v>
+      </c>
+      <c r="G41" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46146</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42" s="2">
+        <v>95179</v>
+      </c>
+      <c r="G42" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="3">
+        <v>45894</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+      <c r="F43" s="2">
+        <v>107124</v>
+      </c>
+      <c r="G43" s="2">
+        <v>119410</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="3">
+        <v>45665</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+      <c r="F44" s="2">
+        <v>69486</v>
+      </c>
+      <c r="G44" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="3">
+        <v>45820</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+      <c r="F45" s="2">
+        <v>63125</v>
+      </c>
+      <c r="G45" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="3">
+        <v>45727</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2">
+        <v>47956</v>
+      </c>
+      <c r="G46" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="3">
+        <v>45935</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" s="2">
+        <v>64383</v>
+      </c>
+      <c r="G47" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+      <c r="F48" s="2">
+        <v>53879</v>
+      </c>
+      <c r="G48" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="3">
+        <v>45741</v>
+      </c>
+      <c r="E49">
+        <v>5</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45252</v>
+      </c>
+      <c r="G49" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="3">
+        <v>45827</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50" s="2">
+        <v>50828</v>
+      </c>
+      <c r="G50" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="3">
+        <v>46197</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+      <c r="F51" s="2">
+        <v>67012</v>
+      </c>
+      <c r="G51" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="3">
+        <v>45965</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52" s="2">
+        <v>57522</v>
+      </c>
+      <c r="G52" s="2">
+        <v>72198</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{410FB2EA-2CD1-4687-A6A4-6ADE1CAF5145}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1307,15 +2595,15 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>3.36</v>
@@ -1323,10 +2611,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>3.18</v>
@@ -1334,10 +2622,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>3.15</v>
@@ -1345,10 +2633,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>3.05</v>
@@ -1356,10 +2644,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>3.05</v>
@@ -1367,10 +2655,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>3.02</v>
@@ -1378,10 +2666,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>2.99</v>
@@ -1389,10 +2677,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>2.98</v>
@@ -1400,10 +2688,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>2.98</v>
@@ -1411,10 +2699,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>2.95</v>
@@ -1425,7 +2713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349F83F1-C6D0-41F2-B7F7-2988D493C800}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1444,7 +2732,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>48</v>
@@ -1455,7 +2743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E101BD-375E-423A-BD31-3FCE0ED5B16F}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1466,15 +2754,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B2">
         <v>51</v>
@@ -1482,7 +2770,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>68</v>
@@ -1490,7 +2778,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>132</v>
@@ -1498,7 +2786,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>134</v>
@@ -1509,7 +2797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFBC8CBA-6D10-40DF-B659-2E36F6DC851C}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1525,25 +2813,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7">
